--- a/bakup/customers/mohammad javad.xlsx
+++ b/bakup/customers/mohammad javad.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="207">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -627,6 +627,39 @@
   </si>
   <si>
     <t>ابمیوه کیک چسپس</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>بستنی اسنک چیپلت</t>
+  </si>
+  <si>
+    <t>1405/06/12</t>
+  </si>
+  <si>
+    <t>بستنی ذغال</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>مداد پاک کن</t>
+  </si>
+  <si>
+    <t>آب</t>
+  </si>
+  <si>
+    <t>1405/07/21</t>
+  </si>
+  <si>
+    <t>تنباکو</t>
+  </si>
+  <si>
+    <t>کمپوت ابمیو</t>
   </si>
 </sst>
 </file>
@@ -754,7 +787,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1131,8 +1185,8 @@
         <v>6</v>
       </c>
       <c r="H2" s="8">
-        <f>B161</f>
-        <v>866500</v>
+        <f>B187</f>
+        <v>2363500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3335,28 +3389,38 @@
     <row r="157" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <f t="shared" si="7"/>
-        <v>866500</v>
-      </c>
-      <c r="B157" s="7"/>
+        <v>1036500</v>
+      </c>
+      <c r="B157" s="7">
+        <v>170000</v>
+      </c>
       <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="1"/>
+      <c r="D157" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="158" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <f t="shared" si="7"/>
-        <v>866500</v>
-      </c>
-      <c r="B158" s="7"/>
+        <v>1321500</v>
+      </c>
+      <c r="B158" s="7">
+        <v>285000</v>
+      </c>
       <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
+      <c r="D158" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="E158" s="1"/>
     </row>
     <row r="159" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8"/>
       <c r="B159" s="8">
         <f>SUM(B139:B158)+B133</f>
-        <v>13281500</v>
+        <v>13736500</v>
       </c>
       <c r="C159" s="8">
         <f>SUM(C139:C158)+C133</f>
@@ -3365,17 +3429,17 @@
       <c r="D159" s="8"/>
     </row>
     <row r="160" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B161" s="11">
         <f>A158</f>
-        <v>866500</v>
+        <v>1321500</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>183</v>
       </c>
       <c r="D161" s="14"/>
     </row>
-    <row r="162" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="13" t="s">
         <v>77</v>
       </c>
@@ -3383,36 +3447,293 @@
         <v>76</v>
       </c>
     </row>
-    <row r="163" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C163" s="2"/>
+    </row>
+    <row r="164" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="7">
+        <f>B161+B165-C165</f>
+        <v>1468500</v>
+      </c>
+      <c r="B165" s="7">
+        <v>147000</v>
+      </c>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="7">
+        <f>A165+B166-C166</f>
+        <v>1538500</v>
+      </c>
+      <c r="B166" s="7">
+        <v>70000</v>
+      </c>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="7">
+        <f>A166+B167-C167</f>
+        <v>1583500</v>
+      </c>
+      <c r="B167" s="7">
+        <v>45000</v>
+      </c>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E167" s="1"/>
+    </row>
+    <row r="168" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="7">
+        <f>A167+B168-C168</f>
+        <v>1833500</v>
+      </c>
+      <c r="B168" s="7">
+        <v>250000</v>
+      </c>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="7">
+        <f>A168+B169-C169</f>
+        <v>2363500</v>
+      </c>
+      <c r="B169" s="7">
+        <v>530000</v>
+      </c>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E169" s="1"/>
+    </row>
+    <row r="170" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="7">
+        <f t="shared" ref="A170" si="8">A169+B170-C170</f>
+        <v>2363500</v>
+      </c>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="1"/>
+    </row>
+    <row r="171" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="7">
+        <f>A170+B171-C171</f>
+        <v>2363500</v>
+      </c>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="1"/>
+    </row>
+    <row r="172" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="7">
+        <f t="shared" ref="A172:A184" si="9">A171+B172-C172</f>
+        <v>2363500</v>
+      </c>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="1"/>
+    </row>
+    <row r="173" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="1"/>
+    </row>
+    <row r="174" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B174" s="7"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="1"/>
+    </row>
+    <row r="175" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="1"/>
+    </row>
+    <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B176" s="7"/>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="1"/>
+    </row>
+    <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="1"/>
+    </row>
+    <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="1"/>
+    </row>
+    <row r="179" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="1"/>
+    </row>
+    <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B180" s="7"/>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="1"/>
+    </row>
+    <row r="181" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="1"/>
+    </row>
+    <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="1"/>
+    </row>
+    <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B183" s="7"/>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="1"/>
+    </row>
+    <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="7">
+        <f t="shared" si="9"/>
+        <v>2363500</v>
+      </c>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="1"/>
+    </row>
+    <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="8"/>
+      <c r="B185" s="8">
+        <f>SUM(B165:B184)+B159</f>
+        <v>14778500</v>
+      </c>
+      <c r="C185" s="8">
+        <f>SUM(C165:C184)+C159</f>
+        <v>12415000</v>
+      </c>
+      <c r="D185" s="8"/>
+    </row>
+    <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="11">
+        <f>A184</f>
+        <v>2363500</v>
+      </c>
+      <c r="C187" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D187" s="14"/>
+    </row>
+    <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B188" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="193" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="194" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="195" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3436,35 +3757,47 @@
     <row r="213" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="214" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="C109:D109"/>
     <mergeCell ref="C135:D135"/>
     <mergeCell ref="C161:D161"/>
+    <mergeCell ref="C187:D187"/>
   </mergeCells>
   <conditionalFormatting sqref="B109">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B135">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B161">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B161">
+  <conditionalFormatting sqref="B187">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
